--- a/dataset/construct/dataset_splits/tum/fold1.xlsx
+++ b/dataset/construct/dataset_splits/tum/fold1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN53"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>324</v>
+        <v>472</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,83 +625,85 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>82.3836315499278</v>
+        <v>82.9967864793267</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>19.2276878705335</v>
       </c>
       <c r="E2" t="n">
-        <v>29.585798816568</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>243</v>
+      </c>
+      <c r="I2" t="n">
+        <v>105</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="K2" t="n">
-        <v>291</v>
+        <v>525</v>
       </c>
       <c r="L2" t="n">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>43</v>
+        <v>31.7</v>
       </c>
       <c r="N2" t="n">
-        <v>455</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>50</v>
+        <v>52.7</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>12</v>
+      </c>
+      <c r="T2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>52</v>
-      </c>
-      <c r="S2" t="n">
-        <v>49</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>20.45</v>
       </c>
       <c r="V2" t="n">
-        <v>53</v>
+        <v>0.14</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>21.1675579322638</v>
       </c>
       <c r="X2" t="n">
-        <v>21.4</v>
+        <v>20.6802165106906</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.238683127572017</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>21.6450216450216</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.9857015385198</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -725,36 +712,27 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>76</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>144</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1427</v>
+        <v>529</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,41 +740,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>86.99098473901689</v>
+        <v>79.79619552817709</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>27.7176852352623</v>
       </c>
       <c r="E3" t="n">
-        <v>25.2080856123662</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>360</v>
+      </c>
+      <c r="I3" t="n">
+        <v>505</v>
+      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>638</v>
       </c>
       <c r="K3" t="n">
-        <v>319.5</v>
+        <v>1503</v>
       </c>
       <c r="L3" t="n">
-        <v>203</v>
+        <v>39</v>
       </c>
       <c r="M3" t="n">
-        <v>264.3</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>786.8</v>
+        <v>78</v>
       </c>
       <c r="O3" t="n">
-        <v>36.6</v>
+        <v>117</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -805,37 +785,37 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>36.6</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>22.15</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X3" t="n">
-        <v>22.35</v>
+        <v>22.1942730679895</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.325842696629214</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.0137509549274</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.1512191514658</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -859,24 +839,15 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>154</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>681</v>
+        <v>321</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -884,123 +855,114 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.1720111795574</v>
+        <v>79.8068831596826</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>24.1684694429421</v>
       </c>
       <c r="E4" t="n">
-        <v>25.9515570934256</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>281</v>
       </c>
       <c r="I4" t="n">
-        <v>451</v>
+        <v>237</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="K4" t="n">
-        <v>190</v>
+        <v>684</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>19</v>
       </c>
       <c r="M4" t="n">
+        <v>27</v>
+      </c>
+      <c r="N4" t="n">
+        <v>27</v>
+      </c>
+      <c r="O4" t="n">
+        <v>73</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W4" t="n">
+        <v>24.1914947797301</v>
+      </c>
+      <c r="X4" t="n">
+        <v>23.6652872775905</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>134</v>
+      </c>
+      <c r="AK4" t="n">
         <v>152</v>
-      </c>
-      <c r="N4" t="n">
-        <v>557</v>
-      </c>
-      <c r="O4" t="n">
-        <v>57</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>11</v>
-      </c>
-      <c r="R4" t="n">
-        <v>68</v>
-      </c>
-      <c r="S4" t="n">
-        <v>49</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>49</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.203921568627451</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>22.5999490705373</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>22.3940969210825</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>367</v>
+        <v>340</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1008,119 +970,114 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82.75246717114101</v>
+        <v>79.8069135485588</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>27.6816608996539</v>
       </c>
       <c r="E5" t="n">
-        <v>27.8520079792239</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>520</v>
+      </c>
+      <c r="I5" t="n">
+        <v>304</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="K5" t="n">
-        <v>378</v>
+        <v>996</v>
       </c>
       <c r="L5" t="n">
-        <v>384</v>
+        <v>18</v>
       </c>
       <c r="M5" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1047</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>25.75</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>25.528393175452</v>
       </c>
       <c r="X5" t="n">
-        <v>23</v>
+        <v>25.055148236001</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.188976377952756</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.9182582123759</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.6484228950307</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>104</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2106</v>
+        <v>1314</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1128,77 +1085,79 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>87.3656652597156</v>
+        <v>79.1469129464852</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>31.833910034602</v>
       </c>
       <c r="E6" t="n">
-        <v>29.0858725761772</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>45</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>120.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>175.9</v>
+      </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>229.1</v>
       </c>
       <c r="K6" t="n">
-        <v>327.7</v>
+        <v>525.5</v>
       </c>
       <c r="L6" t="n">
-        <v>332.3</v>
+        <v>35.9</v>
       </c>
       <c r="M6" t="n">
-        <v>320.1</v>
+        <v>28.7</v>
       </c>
       <c r="N6" t="n">
-        <v>980.1</v>
+        <v>27.5</v>
       </c>
       <c r="O6" t="n">
-        <v>19.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>58.5</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>24.2869875222816</v>
       </c>
       <c r="X6" t="n">
-        <v>27.45</v>
+        <v>23.3675988578761</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.26813880126183</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>27.0244461420932</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>26.4032150535234</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1225,22 +1184,13 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>112</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>621</v>
+        <v>530</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1248,88 +1198,88 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>90.7882052817705</v>
+        <v>84.5046505437676</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>24.3374797187669</v>
       </c>
       <c r="E7" t="n">
-        <v>28.734672057202</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>455</v>
       </c>
       <c r="I7" t="n">
-        <v>1920</v>
+        <v>31</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="K7" t="n">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="L7" t="n">
-        <v>430</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1410</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="P7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>185</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X7" t="n">
-        <v>26.4</v>
+        <v>23.176170013362</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.216216216216216</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>26.4196587726</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>25.8994624442976</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1338,33 +1288,22 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>214</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2131</v>
+        <v>1550</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1372,77 +1311,79 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>91.6978407420083</v>
+        <v>84.8388366986083</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>30.4866850321395</v>
       </c>
       <c r="E8" t="n">
-        <v>24.0569347455645</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>110.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>49</v>
+      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>297.5</v>
+        <v>236</v>
       </c>
       <c r="L8" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>575.2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1238.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>86.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>93.3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>110.9</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>110.9</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>23.332060096766</v>
       </c>
       <c r="X8" t="n">
-        <v>24.9</v>
+        <v>22.7605444857119</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.246478873239437</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>24.7644512350395</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>24.2811760572589</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1460,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -1469,22 +1410,13 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
         <v>120</v>
       </c>
-      <c r="AN8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>329</v>
+        <v>640</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1492,121 +1424,112 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85.28495902730251</v>
+        <v>77.96938740588639</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>21.7192501143118</v>
       </c>
       <c r="E9" t="n">
-        <v>21.484375</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>55</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="I9" t="n">
+        <v>50</v>
+      </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="K9" t="n">
-        <v>74</v>
+        <v>236</v>
       </c>
       <c r="L9" t="n">
-        <v>170</v>
+        <v>22</v>
       </c>
       <c r="M9" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="P9" t="n">
-        <v>51</v>
+        <v>6.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>10</v>
+        <v>23.7</v>
       </c>
       <c r="V9" t="n">
-        <v>23</v>
+        <v>0.23</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X9" t="n">
-        <v>22.13</v>
+        <v>23.3403480044564</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.275136399064692</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.9633307868602</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.406057760656</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>120</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>336</v>
+        <v>1025</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1614,80 +1537,82 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.0155395213831</v>
+        <v>85.2467825500038</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>30.3460743801652</v>
       </c>
       <c r="E10" t="n">
-        <v>19.7231833910034</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>242.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>371.3</v>
+      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>285.3</v>
       </c>
       <c r="K10" t="n">
-        <v>652</v>
+        <v>899.4000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>918</v>
+        <v>72.3</v>
       </c>
       <c r="M10" t="n">
-        <v>547</v>
+        <v>106.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2117</v>
+        <v>85.3</v>
       </c>
       <c r="O10" t="n">
-        <v>95</v>
+        <v>264.3</v>
       </c>
       <c r="P10" t="n">
-        <v>157</v>
+        <v>22.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>344</v>
+        <v>53.2</v>
       </c>
       <c r="S10" t="n">
-        <v>32</v>
+        <v>75.80000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>88</v>
+        <v>26.9</v>
       </c>
       <c r="V10" t="n">
-        <v>142</v>
+        <v>0.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>27.1836007130125</v>
       </c>
       <c r="X10" t="n">
-        <v>26.4</v>
+        <v>26.8217134966894</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.204081632653061</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>27.0562770562771</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>26.6741965227618</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1696,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1711,24 +1636,13 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>162</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>186</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="AK10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>496</v>
+        <v>1572</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1736,88 +1650,88 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74.640161672624</v>
+        <v>86.5638272872462</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>24.8015873015873</v>
       </c>
       <c r="E11" t="n">
-        <v>29.7265160523186</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>37</v>
+        <v>117.8</v>
       </c>
       <c r="I11" t="n">
-        <v>8130</v>
+        <v>166</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>264.6</v>
       </c>
       <c r="K11" t="n">
-        <v>696</v>
+        <v>548.4000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>233</v>
+        <v>7.3</v>
       </c>
       <c r="M11" t="n">
-        <v>339</v>
+        <v>40.5</v>
       </c>
       <c r="N11" t="n">
-        <v>1268</v>
+        <v>18.4</v>
       </c>
       <c r="O11" t="n">
-        <v>131</v>
+        <v>66.19999999999999</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>133</v>
+        <v>19.1</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>19.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>45</v>
+        <v>24.4</v>
       </c>
       <c r="V11" t="n">
-        <v>120</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>24.5098039215686</v>
       </c>
       <c r="X11" t="n">
-        <v>27.2</v>
+        <v>24.1181250506758</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.198675496688742</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>26.7379679144385</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>26.4345313179585</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1835,22 +1749,15 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>112</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
+        <v>192</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2093</v>
+        <v>2217</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1858,85 +1765,85 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>84.1487284521003</v>
+        <v>82.77436832965751</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>20.6131310030261</v>
       </c>
       <c r="E12" t="n">
-        <v>29.0174471992653</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>51</v>
+        <v>348.5</v>
       </c>
       <c r="I12" t="n">
-        <v>5510</v>
+        <v>31.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="K12" t="n">
-        <v>489.6</v>
+        <v>518.6</v>
       </c>
       <c r="L12" t="n">
-        <v>405.5</v>
+        <v>205.1</v>
       </c>
       <c r="M12" t="n">
-        <v>217.9</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1113</v>
+        <v>78.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>283.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>109.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>15.1</v>
+        <v>170.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>279.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>23.75</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>24.0005092946269</v>
       </c>
       <c r="X12" t="n">
-        <v>23.95</v>
+        <v>23.39481796886</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.353951890034364</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.9686783804431</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>22.9720679092787</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -1945,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -1957,24 +1864,15 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>108</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>204</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>700</v>
+        <v>615</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1982,82 +1880,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>86.8191345349456</v>
+        <v>73.3180274799098</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>28.0379234593594</v>
       </c>
       <c r="E13" t="n">
-        <v>25.6055363321799</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
-      </c>
-      <c r="I13" t="n">
-        <v>965</v>
-      </c>
+        <v>783</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>420</v>
-      </c>
+        <v>684</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>285</v>
-      </c>
-      <c r="M13" t="n">
-        <v>308</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>1013</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>23.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X13" t="n">
-        <v>23.8</v>
+        <v>23.4491614055397</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.196969696969697</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>23.554876496053</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>23.4220054480732</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2069,10 +1955,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2081,24 +1967,15 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>190</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2413</v>
+        <v>2488</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2106,79 +1983,79 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>83.4834113494055</v>
+        <v>86.902992211068</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>23.191094619666</v>
       </c>
       <c r="E14" t="n">
-        <v>37.6542220797949</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>60</v>
+        <v>55.2</v>
       </c>
       <c r="I14" t="n">
-        <v>425</v>
+        <v>37.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>28.1</v>
       </c>
       <c r="K14" t="n">
-        <v>1003.9</v>
+        <v>120.6</v>
       </c>
       <c r="L14" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
         <v>22.2</v>
       </c>
-      <c r="N14" t="n">
-        <v>1109.1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>22.0588235294118</v>
       </c>
       <c r="X14" t="n">
-        <v>22.55</v>
+        <v>21.7540506465255</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.285171102661597</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>23.1729055258467</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.6034185328367</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2193,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -2205,24 +2082,15 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>162</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>220</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>954</v>
+        <v>1345</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2230,82 +2098,82 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>78.7770593771389</v>
+        <v>77.4494138971278</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>24.3374797187669</v>
       </c>
       <c r="E15" t="n">
-        <v>28.2283864654296</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>55</v>
+        <v>40.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1580</v>
+        <v>36.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="K15" t="n">
-        <v>488</v>
+        <v>84.5</v>
       </c>
       <c r="L15" t="n">
-        <v>578</v>
+        <v>4.7</v>
       </c>
       <c r="M15" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1452</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
-        <v>111</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>36</v>
+        <v>23.7</v>
       </c>
       <c r="V15" t="n">
-        <v>92</v>
+        <v>0.21</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>23.8413547237077</v>
       </c>
       <c r="X15" t="n">
-        <v>23.05</v>
+        <v>23.506086798771</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.19921875</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>23.2365673542144</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.8163986665956</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2314,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2326,27 +2194,16 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN15" t="n">
         <v>164</v>
       </c>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>662</v>
+        <v>344</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2354,123 +2211,114 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>82.8652711232793</v>
+        <v>85.91221886328491</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>25.8805706350208</v>
       </c>
       <c r="E16" t="n">
-        <v>26.0422405876951</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>432</v>
       </c>
       <c r="I16" t="n">
-        <v>10800</v>
+        <v>378</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="K16" t="n">
-        <v>169</v>
+        <v>1013</v>
       </c>
       <c r="L16" t="n">
-        <v>515</v>
+        <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>306</v>
+        <v>37</v>
       </c>
       <c r="N16" t="n">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="O16" t="n">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="P16" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>28.9661319073084</v>
       </c>
       <c r="X16" t="n">
-        <v>25.1</v>
+        <v>28.6082260699118</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.154411764705882</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>25.4647313470843</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>25.0500676016111</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>184</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2478,40 +2326,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>84.7838999163434</v>
+        <v>84.7733230663929</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>20.829995193078</v>
       </c>
       <c r="E17" t="n">
-        <v>21.4532871972318</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="I17" t="n">
-        <v>365</v>
+        <v>75</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>15.8</v>
       </c>
       <c r="K17" t="n">
-        <v>158</v>
+        <v>283.8</v>
       </c>
       <c r="L17" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2529,28 +2377,28 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>22.7</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>22.7909345556404</v>
       </c>
       <c r="X17" t="n">
-        <v>20.65</v>
+        <v>22.4508627838174</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.3717850776674</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.307569474639</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2565,36 +2413,25 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>162</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="AK17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1776</v>
+        <v>2246</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2602,86 +2439,88 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>82.5145346604305</v>
+        <v>76.92898734377771</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>22.7244034844085</v>
       </c>
       <c r="E18" t="n">
-        <v>22.9130330700044</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>225.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>178.6</v>
+      </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>267.7</v>
       </c>
       <c r="K18" t="n">
-        <v>742.3</v>
+        <v>671.5999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>555.2</v>
+        <v>25.6</v>
       </c>
       <c r="M18" t="n">
-        <v>535.8</v>
+        <v>90.3</v>
       </c>
       <c r="N18" t="n">
-        <v>1833.3</v>
+        <v>96</v>
       </c>
       <c r="O18" t="n">
-        <v>22.7</v>
+        <v>211.9</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>174.3</v>
+        <v>54.7</v>
       </c>
       <c r="R18" t="n">
-        <v>197</v>
+        <v>63.1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>117.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>147.7</v>
+        <v>24.5</v>
       </c>
       <c r="V18" t="n">
-        <v>147.7</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>24.6052966641202</v>
       </c>
       <c r="X18" t="n">
-        <v>25.85</v>
+        <v>23.9831715115263</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.179577464788732</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>26.0058568882098</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>25.6872693127872</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2690,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -2699,24 +2538,15 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>248</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2607</v>
+        <v>1228</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2724,43 +2554,43 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>81.77774745227769</v>
+        <v>85.5069068623723</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>32.4556777151202</v>
       </c>
       <c r="E19" t="n">
-        <v>28.1969212010364</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>56</v>
+        <v>39.8</v>
       </c>
       <c r="I19" t="n">
-        <v>536</v>
+        <v>30.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>26.9</v>
       </c>
       <c r="K19" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="L19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2769,34 +2599,34 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>21.55</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>0.34</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X19" t="n">
-        <v>23.5</v>
+        <v>21.3554558707986</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.272058823529412</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.5867074102368</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8860247016979</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2817,30 +2647,21 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN19" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>645</v>
+        <v>688</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2848,85 +2669,85 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>85.26030306487181</v>
+        <v>86.5826564757776</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>28.7639710716633</v>
       </c>
       <c r="E20" t="n">
-        <v>23.2334561768947</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>480</v>
       </c>
       <c r="I20" t="n">
-        <v>196</v>
+        <v>240.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>281.9</v>
       </c>
       <c r="K20" t="n">
-        <v>114</v>
+        <v>1002.1</v>
       </c>
       <c r="L20" t="n">
-        <v>145</v>
+        <v>46.7</v>
       </c>
       <c r="M20" t="n">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="N20" t="n">
-        <v>389</v>
+        <v>37.1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>104.8</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>42</v>
+        <v>22.25</v>
       </c>
       <c r="V20" t="n">
-        <v>42</v>
+        <v>0.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>22.2498090145149</v>
       </c>
       <c r="X20" t="n">
-        <v>21.4</v>
+        <v>22.0244421422418</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.238683127572017</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.6450216450216</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.2868030290747</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -2935,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -2947,24 +2768,15 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>72</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>238</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>355</v>
+        <v>603</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2972,86 +2784,88 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>93.53169315790809</v>
+        <v>77.0139021978858</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>37.2536452491587</v>
       </c>
       <c r="E21" t="n">
-        <v>24.0344071512902</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>656</v>
+      </c>
+      <c r="I21" t="n">
+        <v>552</v>
+      </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>193</v>
       </c>
       <c r="K21" t="n">
-        <v>141</v>
+        <v>1401</v>
       </c>
       <c r="L21" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="M21" t="n">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="N21" t="n">
-        <v>429</v>
+        <v>13</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Q21" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>40</v>
+        <v>24.9</v>
       </c>
       <c r="V21" t="n">
-        <v>40</v>
+        <v>0.15</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>26.1013496307614</v>
       </c>
       <c r="X21" t="n">
-        <v>22.9</v>
+        <v>25.0246489572143</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.2109375</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>23.2365673542144</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>22.9276988327862</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3060,33 +2874,24 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>196</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>467</v>
+        <v>313</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3094,79 +2899,79 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>80.3545252490684</v>
+        <v>70.8157687213223</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>32.9506802721088</v>
       </c>
       <c r="E22" t="n">
-        <v>34.7222222222222</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>60</v>
+        <v>281</v>
       </c>
       <c r="I22" t="n">
-        <v>2780</v>
+        <v>178</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>281</v>
       </c>
       <c r="K22" t="n">
-        <v>319</v>
+        <v>740</v>
       </c>
       <c r="L22" t="n">
-        <v>274</v>
+        <v>34</v>
       </c>
       <c r="M22" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>905</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="P22" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Q22" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>27.1836007130125</v>
       </c>
       <c r="X22" t="n">
-        <v>29</v>
+        <v>26.8928021808611</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.27893175074184</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>28.9661319073084</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>28.31755269249</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3175,10 +2980,10 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3193,22 +2998,15 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN22" t="inlineStr"/>
+        <v>126</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>624</v>
+        <v>543</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3216,43 +3014,43 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>90.1065803483155</v>
+        <v>82.9988288082744</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>26.7697798929208</v>
       </c>
       <c r="E23" t="n">
-        <v>20.0288415318058</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="I23" t="n">
-        <v>3390</v>
+        <v>125</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="K23" t="n">
-        <v>70</v>
+        <v>343</v>
       </c>
       <c r="L23" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>156</v>
+        <v>37</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -3261,34 +3059,34 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>23.0774127832951</v>
       </c>
       <c r="X23" t="n">
-        <v>22.15</v>
+        <v>22.2229293395349</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.296153846153846</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>22.5999490705373</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>21.9926337013585</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3303,36 +3101,25 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>200</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="AK23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1131</v>
+        <v>1962</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3340,91 +3127,91 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>84.27193794838639</v>
+        <v>74.1123504322255</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>25.0593070266296</v>
       </c>
       <c r="E24" t="n">
-        <v>28.2283864654296</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>60</v>
+        <v>783.1</v>
       </c>
       <c r="I24" t="n">
-        <v>2740</v>
+        <v>744.9</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="K24" t="n">
-        <v>151</v>
+        <v>1697</v>
       </c>
       <c r="L24" t="n">
-        <v>171</v>
+        <v>0.4</v>
       </c>
       <c r="M24" t="n">
-        <v>116</v>
+        <v>196.2</v>
       </c>
       <c r="N24" t="n">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>196.6</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>28.15</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>28.5841609371021</v>
       </c>
       <c r="X24" t="n">
-        <v>25.15</v>
+        <v>28.1846427181971</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.235087719298246</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>25.4647313470843</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>24.8459903311873</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3433,28 +3220,21 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN24" t="inlineStr"/>
+        <v>156</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2319</v>
+        <v>1429</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3462,46 +3242,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>77.2493207024615</v>
+        <v>89.07960906406061</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>36.71875</v>
       </c>
       <c r="E25" t="n">
-        <v>28.515625</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>60</v>
+        <v>522.4</v>
       </c>
       <c r="I25" t="n">
-        <v>348</v>
+        <v>255.8</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>169.8</v>
       </c>
       <c r="K25" t="n">
-        <v>55.8</v>
+        <v>948</v>
       </c>
       <c r="L25" t="n">
-        <v>46.7</v>
+        <v>89.5</v>
       </c>
       <c r="M25" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>117.4</v>
+        <v>28.3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>117.8</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -3510,31 +3290,31 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>23.45</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>23.7458619811561</v>
       </c>
       <c r="X25" t="n">
-        <v>22.8</v>
+        <v>23.6114412754479</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.197628458498024</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.5362872421696</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.1741916431478</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3543,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3555,30 +3335,21 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1205</v>
+        <v>551</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3586,123 +3357,114 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>77.3262297196238</v>
+        <v>86.878606738155</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>23.1481481481481</v>
       </c>
       <c r="E26" t="n">
-        <v>21.09375</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>60</v>
+        <v>852</v>
       </c>
       <c r="I26" t="n">
-        <v>1550</v>
+        <v>377</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>892</v>
       </c>
       <c r="K26" t="n">
-        <v>242</v>
+        <v>2121</v>
       </c>
       <c r="L26" t="n">
-        <v>26</v>
+        <v>300</v>
       </c>
       <c r="M26" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N26" t="n">
-        <v>308</v>
+        <v>204</v>
       </c>
       <c r="O26" t="n">
-        <v>37</v>
+        <v>552</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>37</v>
+        <v>204</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>474</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X26" t="n">
-        <v>20.8</v>
+        <v>23.5033791921504</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.15929203539823</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.3267125031831</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.8945249963572</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>180</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>937</v>
+        <v>977</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3710,82 +3472,82 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>81.4197179443304</v>
+        <v>75.4642704134662</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>23.7196092506476</v>
       </c>
       <c r="E27" t="n">
-        <v>22.0580511886838</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>40</v>
+        <v>663.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2590</v>
+        <v>413.8</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>672</v>
       </c>
       <c r="K27" t="n">
-        <v>177</v>
+        <v>1749.7</v>
       </c>
       <c r="L27" t="n">
-        <v>167</v>
+        <v>32.2</v>
       </c>
       <c r="M27" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>377</v>
+        <v>181</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>213.2</v>
       </c>
       <c r="P27" t="n">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>10</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>76.8</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>26.55</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>27.6928953399542</v>
       </c>
       <c r="X27" t="n">
-        <v>22.45</v>
+        <v>27.2641439526698</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.204</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.2816399286988</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.0792760606539</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3794,39 +3556,30 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>156</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3834,85 +3587,91 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>73.3180274799098</v>
+        <v>85.82740633001239</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>29.0659268067115</v>
       </c>
       <c r="E28" t="n">
-        <v>28.0379234593594</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>60</v>
+        <v>1675</v>
       </c>
       <c r="I28" t="n">
-        <v>479</v>
+        <v>1134</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>1007</v>
       </c>
       <c r="K28" t="n">
-        <v>783</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
+        <v>3816</v>
+      </c>
+      <c r="L28" t="n">
+        <v>371</v>
+      </c>
       <c r="M28" t="n">
-        <v>684</v>
+        <v>124</v>
       </c>
       <c r="N28" t="n">
-        <v>1467</v>
+        <v>316</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
+        <v>811</v>
+      </c>
+      <c r="P28" t="n">
+        <v>155</v>
+      </c>
       <c r="Q28" t="n">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="R28" t="n">
-        <v>86</v>
+        <v>191</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="inlineStr"/>
+        <v>358</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
       <c r="U28" t="n">
-        <v>24</v>
+        <v>26.4</v>
       </c>
       <c r="V28" t="n">
-        <v>24</v>
+        <v>0.16</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>26.4196587726</v>
       </c>
       <c r="X28" t="n">
-        <v>23.25</v>
+        <v>26.3138801572997</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.102040816326531</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>23.4491614055397</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -3921,30 +3680,21 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>104</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>212</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>563</v>
+        <v>306</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3952,79 +3702,79 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>78.34722792607801</v>
+        <v>82.1829412566228</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>21.2305720237141</v>
       </c>
       <c r="E29" t="n">
-        <v>28.6726260752234</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I29" t="n">
-        <v>3150</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="K29" t="n">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c r="L29" t="n">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1073</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="W29" t="n">
-        <v>2</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X29" t="n">
-        <v>23.35</v>
+        <v>22.8721164508225</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.217557251908397</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>23.4111342451446</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4039,36 +3789,23 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>210</v>
-      </c>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -4076,79 +3813,79 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>82.85644725834661</v>
+        <v>88.2965738839455</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>32.8731097961867</v>
       </c>
       <c r="E30" t="n">
-        <v>24.6530314097881</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I30" t="n">
-        <v>4570</v>
+        <v>82</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="K30" t="n">
-        <v>193</v>
+        <v>314</v>
       </c>
       <c r="L30" t="n">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="M30" t="n">
-        <v>321</v>
+        <v>15</v>
       </c>
       <c r="N30" t="n">
-        <v>747</v>
+        <v>58</v>
       </c>
       <c r="O30" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="P30" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>106</v>
+        <v>20.6</v>
       </c>
       <c r="V30" t="n">
-        <v>148</v>
+        <v>0.32</v>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>20.690094219506</v>
       </c>
       <c r="X30" t="n">
-        <v>21.9</v>
+        <v>19.8639809247436</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.308880308880309</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.8678380443086</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.6802165106906</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4163,36 +3900,27 @@
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2868</v>
+        <v>2008</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4200,79 +3928,79 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>79.58796220244891</v>
+        <v>86.27327024235051</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>26.4462809917355</v>
       </c>
       <c r="E31" t="n">
-        <v>23.4375</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>52</v>
+        <v>245.9</v>
       </c>
       <c r="I31" t="n">
-        <v>12100</v>
+        <v>53.9</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>59.7</v>
       </c>
       <c r="K31" t="n">
-        <v>718</v>
+        <v>359.5</v>
       </c>
       <c r="L31" t="n">
-        <v>370</v>
+        <v>46.7</v>
       </c>
       <c r="M31" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1444</v>
+        <v>16.1</v>
       </c>
       <c r="O31" t="n">
-        <v>11</v>
+        <v>62.8</v>
       </c>
       <c r="P31" t="n">
-        <v>27</v>
+        <v>6.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="T31" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>23.75</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>0.21</v>
       </c>
       <c r="W31" t="n">
-        <v>2</v>
+        <v>23.6822001527884</v>
       </c>
       <c r="X31" t="n">
-        <v>22.3</v>
+        <v>23.3621512301397</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.244094488188976</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>23.3638910109498</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>22.8359153550381</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -4287,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -4299,22 +4027,13 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>109</v>
-      </c>
-      <c r="AN31" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="AK31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4322,123 +4041,114 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>85.2440515755317</v>
+        <v>74.7334821722818</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>30.1102788964582</v>
       </c>
       <c r="E32" t="n">
-        <v>21.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
+        <v>575</v>
+      </c>
+      <c r="I32" t="n">
+        <v>273</v>
+      </c>
+      <c r="J32" t="n">
+        <v>224</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1072</v>
+      </c>
+      <c r="L32" t="n">
+        <v>16</v>
+      </c>
+      <c r="M32" t="n">
+        <v>60</v>
+      </c>
+      <c r="N32" t="n">
+        <v>29</v>
+      </c>
+      <c r="O32" t="n">
+        <v>105</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>18</v>
       </c>
-      <c r="I32" t="n">
-        <v>29100</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>166</v>
-      </c>
-      <c r="L32" t="n">
-        <v>24</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>18</v>
       </c>
-      <c r="N32" t="n">
-        <v>208</v>
-      </c>
-      <c r="O32" t="n">
-        <v>4</v>
-      </c>
-      <c r="P32" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>17</v>
-      </c>
-      <c r="S32" t="n">
-        <v>17</v>
-      </c>
       <c r="T32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>24.35</v>
       </c>
       <c r="V32" t="n">
-        <v>24</v>
+        <v>0.16</v>
       </c>
       <c r="W32" t="n">
-        <v>2</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X32" t="n">
-        <v>20.3</v>
+        <v>23.7726133940886</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.234782608695652</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>20.3717850776674</v>
+        <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>20.1186577456453</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>551</v>
+        <v>2012</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4446,88 +4156,88 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>86.878606738155</v>
+        <v>84.8005503270211</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>25.5102040816326</v>
       </c>
       <c r="E33" t="n">
-        <v>23.1481481481481</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>60</v>
+        <v>564.9</v>
       </c>
       <c r="I33" t="n">
-        <v>1010</v>
+        <v>316.7</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>120.3</v>
       </c>
       <c r="K33" t="n">
-        <v>852</v>
+        <v>1001.9</v>
       </c>
       <c r="L33" t="n">
-        <v>377</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>892</v>
+        <v>6.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2121</v>
+        <v>15.3</v>
       </c>
       <c r="O33" t="n">
-        <v>300</v>
+        <v>116.3</v>
       </c>
       <c r="P33" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>204</v>
+        <v>24.85</v>
       </c>
       <c r="V33" t="n">
-        <v>474</v>
+        <v>0.35</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>25.9103641456583</v>
       </c>
       <c r="X33" t="n">
-        <v>23.7</v>
+        <v>24.8126692377086</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.197718631178707</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>23.5033791921504</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4536,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
@@ -4545,24 +4255,15 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>76</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>234</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1849</v>
+        <v>1776</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4570,88 +4271,88 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>79.69184339113239</v>
+        <v>82.5145346604305</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>22.9130330700044</v>
       </c>
       <c r="E34" t="n">
-        <v>25.9259259259259</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>60</v>
+        <v>742.3</v>
       </c>
       <c r="I34" t="n">
-        <v>2230</v>
+        <v>555.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>535.8</v>
       </c>
       <c r="K34" t="n">
-        <v>417</v>
+        <v>1833.3</v>
       </c>
       <c r="L34" t="n">
-        <v>426</v>
+        <v>22.7</v>
       </c>
       <c r="M34" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1045</v>
+        <v>174.3</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>8</v>
+        <v>147.7</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>147.7</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>25.85</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>26.0058568882098</v>
       </c>
       <c r="X34" t="n">
-        <v>26.35</v>
+        <v>25.6872693127872</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.207482993197279</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>26.1013496307614</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>25.8994624442976</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4660,31 +4361,24 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>124</v>
-      </c>
-      <c r="AN34" t="inlineStr"/>
+        <v>248</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>461</v>
+        <v>1154</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4692,79 +4386,79 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>84.5707518632596</v>
+        <v>84.58157277486249</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>23.7654320987654</v>
       </c>
       <c r="E35" t="n">
-        <v>24.2214532871972</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>18</v>
+        <v>274.1</v>
       </c>
       <c r="I35" t="n">
-        <v>28200</v>
+        <v>300.4</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>298.1</v>
       </c>
       <c r="K35" t="n">
-        <v>484</v>
+        <v>872.6</v>
       </c>
       <c r="L35" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>864</v>
+        <v>31.1</v>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>31.1</v>
       </c>
       <c r="P35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>28.2</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>28.4568372803667</v>
       </c>
       <c r="X35" t="n">
-        <v>27.95</v>
+        <v>28.0442958618834</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.247648902821317</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>28.3295136236313</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>27.8644426146005</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -4773,10 +4467,10 @@
         <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -4791,112 +4485,105 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>168</v>
-      </c>
-      <c r="AN35" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="AK35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>362</v>
+        <v>508</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>78.7965795878013</v>
+        <v>64.8304449641291</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>25.7909680908599</v>
       </c>
       <c r="E36" t="n">
-        <v>30.2595039739538</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>20</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
+        <v>841</v>
+      </c>
+      <c r="I36" t="n">
+        <v>198</v>
+      </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="K36" t="n">
-        <v>471</v>
+        <v>1166</v>
       </c>
       <c r="L36" t="n">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="M36" t="n">
-        <v>194</v>
+        <v>9</v>
       </c>
       <c r="N36" t="n">
-        <v>855</v>
+        <v>12</v>
       </c>
       <c r="O36" t="n">
-        <v>58</v>
+        <v>196</v>
       </c>
       <c r="P36" t="n">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="Q36" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>17</v>
+        <v>28.65</v>
       </c>
       <c r="V36" t="n">
-        <v>37</v>
+        <v>0.23</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>29.1571173924115</v>
       </c>
       <c r="X36" t="n">
-        <v>26.65</v>
+        <v>28.6748861045274</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.252459016393443</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>28.0112044817927</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>26.4585955298766</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -4911,110 +4598,99 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>184</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AK36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>585</v>
+        <v>672</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>75.1550840368089</v>
+        <v>84.077751159784</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>23.3234180638182</v>
       </c>
       <c r="E37" t="n">
-        <v>27.1706315662359</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>40</v>
+        <v>701.4</v>
       </c>
       <c r="I37" t="n">
-        <v>8750</v>
+        <v>213.8</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>169.8</v>
       </c>
       <c r="K37" t="n">
-        <v>331</v>
+        <v>1085</v>
       </c>
       <c r="L37" t="n">
-        <v>96</v>
+        <v>35.9</v>
       </c>
       <c r="M37" t="n">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>699</v>
+        <v>33.3</v>
       </c>
       <c r="O37" t="n">
-        <v>46</v>
+        <v>69.19999999999999</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>121</v>
+        <v>6.9</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>23.75</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>24.3188184364655</v>
       </c>
       <c r="X37" t="n">
-        <v>26.7</v>
+        <v>23.7002215763568</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.434017595307918</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>28.4250063661828</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>26.6503269908915</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5023,238 +4699,220 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN37" t="inlineStr"/>
+        <v>170</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1386</v>
+        <v>1736</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>79.1220757598803</v>
+        <v>86.46788494689081</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>24.8579545454545</v>
       </c>
       <c r="E38" t="n">
-        <v>30.8444159589809</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>60</v>
+        <v>187.8</v>
       </c>
       <c r="I38" t="n">
-        <v>269</v>
+        <v>186.2</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>239</v>
       </c>
       <c r="K38" t="n">
-        <v>141.1</v>
+        <v>613</v>
       </c>
       <c r="L38" t="n">
-        <v>73.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>64.2</v>
+        <v>19.5</v>
       </c>
       <c r="N38" t="n">
-        <v>278.7</v>
+        <v>13.8</v>
       </c>
       <c r="O38" t="n">
-        <v>6.5</v>
+        <v>33.3</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>27.2</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W38" t="n">
-        <v>2</v>
+        <v>27.3745861981156</v>
       </c>
       <c r="X38" t="n">
-        <v>22.75</v>
+        <v>26.9117274486368</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>22.9819200407436</v>
+        <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>22.6793115897943</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>104</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>200</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AK38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>506</v>
+        <v>605</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>83.28082363677851</v>
+        <v>73.8847250741501</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>29.3847566574839</v>
       </c>
       <c r="E39" t="n">
-        <v>24.6913580246913</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>60</v>
+        <v>321</v>
       </c>
       <c r="I39" t="n">
-        <v>1790</v>
+        <v>617</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="K39" t="n">
-        <v>349.5</v>
+        <v>1042</v>
       </c>
       <c r="L39" t="n">
-        <v>410.7</v>
+        <v>64</v>
       </c>
       <c r="M39" t="n">
-        <v>277.3</v>
+        <v>88</v>
       </c>
       <c r="N39" t="n">
-        <v>1037.5</v>
+        <v>20</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q39" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>14.5</v>
+        <v>33</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>19.4168576521518</v>
       </c>
       <c r="X39" t="n">
-        <v>24.9</v>
+        <v>19.1461601132455</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.246478873239437</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>24.9554367201426</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>24.4118755484088</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -5275,30 +4933,21 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>106</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2246</v>
+        <v>474</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5306,77 +4955,79 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>76.92898734377771</v>
+        <v>78.2075977577509</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>27.6816608996539</v>
       </c>
       <c r="E40" t="n">
-        <v>22.7244034844085</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>49</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
+        <v>187</v>
+      </c>
+      <c r="I40" t="n">
+        <v>222</v>
+      </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="K40" t="n">
-        <v>225.3</v>
+        <v>630</v>
       </c>
       <c r="L40" t="n">
-        <v>178.6</v>
+        <v>11</v>
       </c>
       <c r="M40" t="n">
-        <v>267.7</v>
+        <v>25</v>
       </c>
       <c r="N40" t="n">
-        <v>671.6</v>
+        <v>23</v>
       </c>
       <c r="O40" t="n">
-        <v>25.6</v>
+        <v>59</v>
       </c>
       <c r="P40" t="n">
-        <v>90.3</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>211.9</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>54.7</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>63.1</v>
+        <v>26.8</v>
       </c>
       <c r="V40" t="n">
-        <v>117.8</v>
+        <v>0.21</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>26.7379679144385</v>
       </c>
       <c r="X40" t="n">
-        <v>24.5</v>
+        <v>26.4345313179585</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.298611111111111</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>24.6052966641202</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>23.9831715115263</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -5388,39 +5039,28 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>114</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>168</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="AK40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>347</v>
+        <v>635</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5428,77 +5068,79 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>84.5302151304282</v>
+        <v>79.51356757167849</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>21.09375</v>
       </c>
       <c r="E41" t="n">
-        <v>27.0416441319632</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>45</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+        <v>523</v>
+      </c>
+      <c r="I41" t="n">
+        <v>178</v>
+      </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="K41" t="n">
-        <v>346</v>
+        <v>980</v>
       </c>
       <c r="L41" t="n">
-        <v>162.8</v>
+        <v>96</v>
       </c>
       <c r="M41" t="n">
-        <v>134.3</v>
+        <v>65</v>
       </c>
       <c r="N41" t="n">
-        <v>643.1</v>
+        <v>58</v>
       </c>
       <c r="O41" t="n">
-        <v>39.2</v>
+        <v>219</v>
       </c>
       <c r="P41" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>48.8</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>8.6</v>
+        <v>23.9</v>
       </c>
       <c r="V41" t="n">
-        <v>46.8</v>
+        <v>0.22</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X41" t="n">
-        <v>26.4</v>
+        <v>23.5844721732425</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.197952218430034</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>26.4196587726</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>26.0831054612881</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
@@ -5516,113 +5158,108 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="AK41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>364</v>
+        <v>607</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>83.7306500177453</v>
+        <v>83.2043843638299</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>30.3673469387755</v>
       </c>
       <c r="E42" t="n">
-        <v>27.639801313892</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>60</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
+        <v>755.3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>348.4</v>
+      </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>608.8</v>
       </c>
       <c r="K42" t="n">
-        <v>186</v>
+        <v>1712.5</v>
       </c>
       <c r="L42" t="n">
-        <v>72</v>
+        <v>42.5</v>
       </c>
       <c r="M42" t="n">
-        <v>31</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>289</v>
+        <v>114.3</v>
       </c>
       <c r="O42" t="n">
-        <v>116</v>
+        <v>232.9</v>
       </c>
       <c r="P42" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="R42" t="n">
-        <v>132</v>
+        <v>48.6</v>
       </c>
       <c r="S42" t="n">
-        <v>22</v>
+        <v>60.5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="V42" t="n">
-        <v>22</v>
+        <v>0.19</v>
       </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>25.4329004329004</v>
       </c>
       <c r="X42" t="n">
-        <v>21.15</v>
+        <v>24.9660878629553</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.301204819277108</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="n">
-        <v>21.3267125031831</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>20.8029488434442</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -5643,22 +5280,15 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN42" t="inlineStr"/>
+        <v>198</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>516</v>
+        <v>2010</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5666,85 +5296,85 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>82.09534185109131</v>
+        <v>84.44497680431969</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>23.0111768573307</v>
       </c>
       <c r="E43" t="n">
-        <v>29.0256076388888</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>50</v>
+        <v>30.6</v>
       </c>
       <c r="I43" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>11.1</v>
       </c>
       <c r="K43" t="n">
-        <v>797</v>
+        <v>41.7</v>
       </c>
       <c r="L43" t="n">
-        <v>410</v>
+        <v>24.5</v>
       </c>
       <c r="M43" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1631</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>133</v>
+        <v>24.5</v>
       </c>
       <c r="P43" t="n">
-        <v>44</v>
+        <v>45.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="T43" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="V43" t="n">
-        <v>9</v>
+        <v>0.21</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>19.4805194805195</v>
       </c>
       <c r="X43" t="n">
-        <v>25</v>
+        <v>19.1826891138042</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.257839721254355</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>25.1464222052457</v>
+        <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>24.6143810163112</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -5756,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
@@ -5765,22 +5395,15 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>194</v>
-      </c>
-      <c r="AN43" t="inlineStr"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2217</v>
+        <v>1109</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5788,121 +5411,114 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>82.77436832965751</v>
+        <v>79.1909800174918</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>28.3937263385613</v>
       </c>
       <c r="E44" t="n">
-        <v>20.6131310030261</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>45</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
+        <v>187</v>
+      </c>
+      <c r="I44" t="n">
+        <v>173</v>
+      </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="K44" t="n">
-        <v>348.5</v>
+        <v>518</v>
       </c>
       <c r="L44" t="n">
-        <v>31.1</v>
+        <v>24</v>
       </c>
       <c r="M44" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>518.6</v>
+        <v>14</v>
       </c>
       <c r="O44" t="n">
-        <v>205.1</v>
+        <v>38</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>78.7</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>283.8</v>
+        <v>33</v>
       </c>
       <c r="S44" t="n">
-        <v>109.1</v>
+        <v>33</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>170.5</v>
+        <v>30</v>
       </c>
       <c r="V44" t="n">
-        <v>279.6</v>
+        <v>0.21</v>
       </c>
       <c r="W44" t="n">
-        <v>2</v>
+        <v>30.2393684746626</v>
       </c>
       <c r="X44" t="n">
-        <v>23.75</v>
+        <v>29.7425256555005</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.297491039426523</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>24.0005092946269</v>
+        <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>23.39481796886</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>158</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>254</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1419</v>
+        <v>959</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5910,41 +5526,43 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>77.95573351585671</v>
+        <v>75.6452314814815</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>19.9510204081632</v>
       </c>
       <c r="E45" t="n">
-        <v>33.0578512396694</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>60</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
+        <v>281</v>
+      </c>
+      <c r="I45" t="n">
+        <v>78</v>
+      </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K45" t="n">
-        <v>31.7</v>
+        <v>394</v>
       </c>
       <c r="L45" t="n">
-        <v>38.6</v>
+        <v>10</v>
       </c>
       <c r="M45" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>82.5</v>
+        <v>5</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -5959,28 +5577,28 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W45" t="n">
-        <v>2</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X45" t="n">
-        <v>20.35</v>
+        <v>22.6203056614775</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.222707423580786</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>20.6582633053221</v>
+        <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>20.3326250911699</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -5995,116 +5613,105 @@
         <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>180</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="AK45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>479</v>
+        <v>796</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>76.58740265419419</v>
+        <v>77.90669860825921</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>28.125</v>
       </c>
       <c r="E46" t="n">
-        <v>23.8086901719127</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>60</v>
+        <v>58.9</v>
       </c>
       <c r="I46" t="n">
-        <v>7630</v>
+        <v>34.8</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>515.7</v>
+        <v>159.1</v>
       </c>
       <c r="L46" t="n">
-        <v>335.7</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>145.7</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>997.1</v>
+        <v>16.8</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="P46" t="n">
-        <v>80.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>80.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>60.9</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>22.15</v>
       </c>
       <c r="V46" t="n">
-        <v>68.59999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>21.9314998726763</v>
       </c>
       <c r="X46" t="n">
-        <v>23.95</v>
+        <v>21.5128218033123</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.157692307692308</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="n">
-        <v>24.4779730073848</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>24.1708423267993</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
@@ -6128,71 +5735,62 @@
         <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>196</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1227</v>
+        <v>1205</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>86.8977646905975</v>
+        <v>77.3262297196238</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>21.09375</v>
       </c>
       <c r="E47" t="n">
-        <v>23.3843537414965</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>60</v>
+        <v>242</v>
       </c>
       <c r="I47" t="n">
-        <v>1140</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K47" t="n">
-        <v>646</v>
+        <v>308</v>
       </c>
       <c r="L47" t="n">
-        <v>212</v>
+        <v>37</v>
       </c>
       <c r="M47" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>973</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -6201,40 +5799,40 @@
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W47" t="n">
-        <v>1</v>
+        <v>21.3267125031831</v>
       </c>
       <c r="X47" t="n">
-        <v>23.2</v>
+        <v>20.8945249963572</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.318840579710145</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>22.9182582123759</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>22.1655797488585</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6252,107 +5850,98 @@
         <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>242</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>936</v>
+        <v>622</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>91.0289564795802</v>
+        <v>89.18695401424699</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>23.2525951557093</v>
       </c>
       <c r="E48" t="n">
-        <v>23.1111111111111</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="I48" t="n">
-        <v>10700</v>
+        <v>349</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>302</v>
       </c>
       <c r="K48" t="n">
-        <v>396</v>
+        <v>813</v>
       </c>
       <c r="L48" t="n">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="M48" t="n">
-        <v>307</v>
+        <v>27</v>
       </c>
       <c r="N48" t="n">
-        <v>851</v>
+        <v>18</v>
       </c>
       <c r="O48" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="P48" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>40</v>
+        <v>27.45</v>
       </c>
       <c r="V48" t="n">
-        <v>40</v>
+        <v>0.26</v>
       </c>
       <c r="W48" t="n">
-        <v>2</v>
+        <v>27.6928953399542</v>
       </c>
       <c r="X48" t="n">
-        <v>20.05</v>
+        <v>26.8406888888731</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.209821428571429</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>20.3717850776674</v>
+        <v>1</v>
       </c>
       <c r="AA48" t="n">
-        <v>19.8319163664306</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
@@ -6361,42 +5950,31 @@
         <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>118</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>178</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="AK48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6404,86 +5982,88 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>81.5341052551525</v>
+        <v>82.8652711232793</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>26.0422405876951</v>
       </c>
       <c r="E49" t="n">
-        <v>26.8687356599444</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>60</v>
+        <v>169</v>
       </c>
       <c r="I49" t="n">
-        <v>7140</v>
+        <v>515</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
       <c r="K49" t="n">
-        <v>484</v>
+        <v>990</v>
       </c>
       <c r="L49" t="n">
-        <v>784</v>
+        <v>27</v>
       </c>
       <c r="M49" t="n">
-        <v>419</v>
+        <v>9</v>
       </c>
       <c r="N49" t="n">
-        <v>1687</v>
+        <v>42</v>
       </c>
       <c r="O49" t="n">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="P49" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
-      <c r="T49" t="inlineStr"/>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>25.1</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>25.4647313470843</v>
       </c>
       <c r="X49" t="n">
-        <v>28.7</v>
+        <v>25.0500676016111</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.271084337349398</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>28.9661319073084</v>
+        <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>28.2049576036652</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -6501,113 +6081,104 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>230</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>568</v>
+        <v>2220</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>80.78428017339721</v>
+        <v>88.7674595659999</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>17.7999288002847</v>
       </c>
       <c r="E50" t="n">
-        <v>36.3321799307958</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>60</v>
+        <v>30.9</v>
       </c>
       <c r="I50" t="n">
-        <v>225</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>19.3</v>
       </c>
       <c r="K50" t="n">
-        <v>229.8</v>
+        <v>56.2</v>
       </c>
       <c r="L50" t="n">
-        <v>233.3</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>398.5</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>861.6</v>
+        <v>7</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P50" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>46.3</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>53.9</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W50" t="n">
-        <v>1</v>
+        <v>20.6582633053221</v>
       </c>
       <c r="X50" t="n">
-        <v>26.15</v>
+        <v>20.4418823263722</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.262458471760797</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>26.8334606569901</v>
+        <v>1</v>
       </c>
       <c r="AA50" t="n">
-        <v>26.0709028381822</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -6622,27 +6193,18 @@
         <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>204</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>600</v>
+        <v>714</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6650,123 +6212,114 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>87.4373393413948</v>
+        <v>86.8923168428524</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>22.6473769605191</v>
       </c>
       <c r="E51" t="n">
-        <v>24.4444444444444</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>60</v>
+        <v>648</v>
       </c>
       <c r="I51" t="n">
-        <v>914</v>
+        <v>498</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>649</v>
       </c>
       <c r="K51" t="n">
-        <v>480</v>
+        <v>1795</v>
       </c>
       <c r="L51" t="n">
-        <v>127</v>
+        <v>263</v>
       </c>
       <c r="M51" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="N51" t="n">
-        <v>741</v>
+        <v>56</v>
       </c>
       <c r="O51" t="n">
-        <v>200</v>
+        <v>441</v>
       </c>
       <c r="P51" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="Q51" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="R51" t="n">
-        <v>236</v>
+        <v>6</v>
       </c>
       <c r="S51" t="n">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>25.75</v>
       </c>
       <c r="V51" t="n">
-        <v>55</v>
+        <v>0.27</v>
       </c>
       <c r="W51" t="n">
-        <v>2</v>
+        <v>25.9103641456583</v>
       </c>
       <c r="X51" t="n">
-        <v>20</v>
+        <v>25.3531036326332</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.214285714285714</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>20.2762923351159</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>19.9151768367782</v>
+        <v>1</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>190</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6774,82 +6327,82 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>88.22278655537809</v>
+        <v>76.58740265419419</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>23.8086901719127</v>
       </c>
       <c r="E52" t="n">
-        <v>31.25</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>55</v>
+        <v>515.7</v>
       </c>
       <c r="I52" t="n">
-        <v>4460</v>
+        <v>335.7</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>145.7</v>
       </c>
       <c r="K52" t="n">
-        <v>490</v>
+        <v>997.1000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>661</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>651</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>1802</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>129</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="P52" t="n">
-        <v>228</v>
+        <v>7.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>183</v>
+        <v>60.9</v>
       </c>
       <c r="R52" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="T52" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>135</v>
+        <v>23.95</v>
       </c>
       <c r="V52" t="n">
-        <v>163</v>
+        <v>0.16</v>
       </c>
       <c r="W52" t="n">
-        <v>2</v>
+        <v>24.4779730073848</v>
       </c>
       <c r="X52" t="n">
-        <v>20.65</v>
+        <v>24.1708423267993</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.15625</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>20.690094219506</v>
+        <v>1</v>
       </c>
       <c r="AA52" t="n">
-        <v>20.4636637734958</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6873,142 +6426,352 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>132</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>170</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2375</v>
+        <v>350</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>no event</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>79.3687013904733</v>
+      </c>
+      <c r="D53" t="n">
+        <v>23.3843537414965</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>20</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>385</v>
+      </c>
+      <c r="I53" t="n">
+        <v>385</v>
+      </c>
+      <c r="J53" t="n">
+        <v>530</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L53" t="n">
+        <v>10</v>
+      </c>
+      <c r="M53" t="n">
+        <v>11</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>21</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>27</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W53" t="n">
+        <v>27.6928953399542</v>
+      </c>
+      <c r="X53" t="n">
+        <v>26.9825789818199</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>126</v>
+      </c>
+      <c r="AK53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>600</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>no event</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>87.4373393413948</v>
+      </c>
+      <c r="D54" t="n">
+        <v>24.4444444444444</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>60</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>480</v>
+      </c>
+      <c r="I54" t="n">
+        <v>127</v>
+      </c>
+      <c r="J54" t="n">
+        <v>134</v>
+      </c>
+      <c r="K54" t="n">
+        <v>741</v>
+      </c>
+      <c r="L54" t="n">
+        <v>200</v>
+      </c>
+      <c r="M54" t="n">
+        <v>15</v>
+      </c>
+      <c r="N54" t="n">
+        <v>21</v>
+      </c>
+      <c r="O54" t="n">
+        <v>236</v>
+      </c>
+      <c r="P54" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>55</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>20</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="W54" t="n">
+        <v>20.2762923351159</v>
+      </c>
+      <c r="X54" t="n">
+        <v>19.9151768367782</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>922</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>pacer</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>85.331470485715</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>23.4567901234567</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="I53" t="n">
-        <v>17300</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>121.2</v>
-      </c>
-      <c r="L53" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="M53" t="n">
-        <v>197.3</v>
-      </c>
-      <c r="N53" t="n">
-        <v>388.1</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="R53" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1</v>
-      </c>
-      <c r="X53" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0.22992700729927</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>24.7326203208556</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>24.3805715703063</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>142</v>
-      </c>
-      <c r="AN53" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>75.0324815258448</v>
+      </c>
+      <c r="D55" t="n">
+        <v>26.4721074380165</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>60</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>280</v>
+      </c>
+      <c r="I55" t="n">
+        <v>391</v>
+      </c>
+      <c r="J55" t="n">
+        <v>306</v>
+      </c>
+      <c r="K55" t="n">
+        <v>977</v>
+      </c>
+      <c r="L55" t="n">
+        <v>16</v>
+      </c>
+      <c r="M55" t="n">
+        <v>31</v>
+      </c>
+      <c r="N55" t="n">
+        <v>32</v>
+      </c>
+      <c r="O55" t="n">
+        <v>79</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="W55" t="n">
+        <v>27.3745861981156</v>
+      </c>
+      <c r="X55" t="n">
+        <v>26.7218716216114</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>86</v>
+      </c>
+      <c r="AK55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
